--- a/utils/monday_sprint_sprint_2025-7.xlsx
+++ b/utils/monday_sprint_sprint_2025-7.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="228">
   <si>
     <t>Ticket</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t>10/02/2025</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
   </si>
   <si>
     <t>Semana 2</t>
@@ -2566,16 +2569,16 @@
         <v>96</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -2592,7 +2595,7 @@
         <v>91</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>93</v>
@@ -2610,21 +2613,21 @@
         <v>96</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2636,10 +2639,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>19</v>
@@ -2668,7 +2671,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -2680,10 +2683,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>19</v>
@@ -2712,7 +2715,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -2724,10 +2727,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>19</v>
@@ -2756,7 +2759,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -2768,10 +2771,10 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>19</v>
@@ -2800,7 +2803,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -2812,10 +2815,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>32</v>
@@ -2844,7 +2847,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -2856,10 +2859,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>19</v>
@@ -2888,7 +2891,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -2900,10 +2903,10 @@
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>19</v>
@@ -2932,7 +2935,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -2944,10 +2947,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>19</v>
@@ -2976,7 +2979,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -2988,10 +2991,10 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>19</v>
@@ -3020,7 +3023,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3032,10 +3035,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
@@ -3076,10 +3079,10 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>19</v>
@@ -3120,10 +3123,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3152,7 +3155,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3164,10 +3167,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3196,7 +3199,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3208,10 +3211,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
@@ -3240,7 +3243,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3252,10 +3255,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3284,7 +3287,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3296,39 +3299,39 @@
         <v>91</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3340,10 +3343,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3372,7 +3375,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3384,22 +3387,22 @@
         <v>91</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>17</v>
@@ -3408,15 +3411,15 @@
         <v>43</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3428,10 +3431,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
@@ -3460,7 +3463,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3472,10 +3475,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>19</v>
@@ -3493,7 +3496,7 @@
         <v>17</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>25</v>
@@ -3504,7 +3507,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3516,10 +3519,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>19</v>
@@ -3548,7 +3551,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3560,10 +3563,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3592,7 +3595,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3604,10 +3607,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
@@ -3636,7 +3639,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3648,10 +3651,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3669,7 +3672,7 @@
         <v>17</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M58" s="2" t="s">
         <v>29</v>
@@ -3680,7 +3683,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3692,10 +3695,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>32</v>
@@ -3724,7 +3727,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -3736,10 +3739,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
@@ -3768,7 +3771,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3780,10 +3783,10 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>32</v>
@@ -3812,7 +3815,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -3824,10 +3827,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>32</v>
@@ -3856,7 +3859,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -3868,10 +3871,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
@@ -3900,7 +3903,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -3912,10 +3915,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -3944,7 +3947,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -3956,10 +3959,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>32</v>
@@ -3977,7 +3980,7 @@
         <v>17</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>25</v>
@@ -3988,7 +3991,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4000,10 +4003,10 @@
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
@@ -4032,7 +4035,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4044,10 +4047,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>32</v>
@@ -4065,7 +4068,7 @@
         <v>17</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M67" s="2" t="s">
         <v>25</v>
@@ -4076,7 +4079,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4088,10 +4091,10 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
@@ -4120,7 +4123,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4132,10 +4135,10 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>32</v>
@@ -4164,7 +4167,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4176,10 +4179,10 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>32</v>
@@ -4208,7 +4211,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4220,10 +4223,10 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>32</v>
@@ -4252,7 +4255,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4264,10 +4267,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>32</v>
@@ -4285,7 +4288,7 @@
         <v>17</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>25</v>
@@ -4296,7 +4299,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4308,10 +4311,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>19</v>
@@ -4340,7 +4343,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4352,10 +4355,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
@@ -4384,7 +4387,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4396,10 +4399,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>32</v>
@@ -4428,7 +4431,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4440,10 +4443,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>32</v>
@@ -4472,7 +4475,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4484,10 +4487,10 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>32</v>
@@ -4528,7 +4531,7 @@
         <v>91</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>93</v>
@@ -4546,16 +4549,16 @@
         <v>96</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
@@ -4572,7 +4575,7 @@
         <v>91</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>93</v>
@@ -4590,16 +4593,16 @@
         <v>96</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
@@ -4616,7 +4619,7 @@
         <v>91</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>93</v>
@@ -4634,16 +4637,16 @@
         <v>96</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
@@ -4660,7 +4663,7 @@
         <v>91</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>93</v>
@@ -4678,16 +4681,16 @@
         <v>96</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
@@ -4704,7 +4707,7 @@
         <v>91</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>93</v>
@@ -4722,16 +4725,16 @@
         <v>96</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
@@ -4748,7 +4751,7 @@
         <v>91</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>93</v>
@@ -4766,36 +4769,36 @@
         <v>96</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>43</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>19</v>
@@ -4824,22 +4827,22 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>19</v>
@@ -4868,22 +4871,22 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>19</v>
@@ -4912,7 +4915,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -4924,10 +4927,10 @@
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>32</v>
@@ -4967,23 +4970,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4991,16 +4994,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5019,7 +5022,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5040,7 +5043,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5071,12 +5074,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B2">
         <v>86</v>
@@ -5100,25 +5103,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5135,13 +5138,13 @@
         <v>62</v>
       </c>
       <c r="G10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5173,7 +5176,7 @@
         <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K11">
         <v>86</v>
@@ -5185,10 +5188,10 @@
         <v>10</v>
       </c>
       <c r="P11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q11">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -5205,7 +5208,7 @@
         <v>69</v>
       </c>
       <c r="M12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -5214,24 +5217,24 @@
         <v>25</v>
       </c>
       <c r="Q12">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N13">
         <v>4</v>
@@ -5243,9 +5246,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5256,16 +5259,10 @@
       <c r="N14">
         <v>11</v>
       </c>
-      <c r="P14" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -5273,7 +5270,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -5281,7 +5278,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5289,7 +5286,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -5300,7 +5297,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5308,7 +5305,7 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
@@ -5317,21 +5314,21 @@
         <v>458</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5342,10 +5339,10 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5356,10 +5353,10 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5370,7 +5367,7 @@
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>187</v>
@@ -5384,7 +5381,7 @@
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>188</v>
@@ -5398,7 +5395,7 @@
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>189</v>
@@ -5412,7 +5409,7 @@
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>190</v>
@@ -5426,7 +5423,7 @@
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>191</v>
@@ -5434,16 +5431,16 @@
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>139</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2025-7.xlsx
+++ b/utils/monday_sprint_sprint_2025-7.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="265">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>30376</t>
+    <t>8648122637</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>07/03/2025</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>05/04/2025</t>
   </si>
   <si>
     <t>Implantação</t>
@@ -102,7 +102,7 @@
     <t>Março</t>
   </si>
   <si>
-    <t>30606</t>
+    <t>8753630027</t>
   </si>
   <si>
     <t>Informação do percentual de refugo por motivo pela quantidade produzida no QlickSense</t>
@@ -111,12 +111,12 @@
     <t>21/03/2025</t>
   </si>
   <si>
+    <t>23/03/2025</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Semana 3</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>30238</t>
+    <t>8764450151</t>
   </si>
   <si>
     <t>QVD - Faturamento (Contas a receber)</t>
@@ -150,28 +150,34 @@
     <t>24/03/2025</t>
   </si>
   <si>
+    <t>06/04/2025</t>
+  </si>
+  <si>
     <t>Testes</t>
   </si>
   <si>
-    <t>30537</t>
+    <t>8753851144</t>
   </si>
   <si>
     <t>Alteração fluxo - Alto impacto workflow</t>
   </si>
   <si>
-    <t>29478</t>
+    <t>8764535877</t>
   </si>
   <si>
     <t>Qlik Sense - Custos de Venda Geral</t>
   </si>
   <si>
-    <t>30424</t>
+    <t>03/04/2025</t>
+  </si>
+  <si>
+    <t>8754444964</t>
   </si>
   <si>
     <t>Melhoria do Dashboard do Sistema 5S</t>
   </si>
   <si>
-    <t>30379</t>
+    <t>8764365492</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -183,13 +189,16 @@
     <t>Feito</t>
   </si>
   <si>
-    <t>30689</t>
+    <t>8751522518</t>
   </si>
   <si>
     <t>Debit memo 029/25</t>
   </si>
   <si>
-    <t>30067</t>
+    <t>25/03/2025</t>
+  </si>
+  <si>
+    <t>8540399372</t>
   </si>
   <si>
     <t>CRIAÇÃO DE SETOR ENGENHARIA DE PRODUTO E APLICAÇÃO</t>
@@ -198,103 +207,118 @@
     <t>21/02/2025</t>
   </si>
   <si>
-    <t>30281</t>
+    <t>27/03/2025</t>
+  </si>
+  <si>
+    <t>8648354003</t>
   </si>
   <si>
     <t>Alteração de tamanho do campo</t>
   </si>
   <si>
-    <t>29870</t>
+    <t>8754860071</t>
   </si>
   <si>
     <t>Apontamentos Inspeção JAN/2025</t>
   </si>
   <si>
-    <t>30287</t>
+    <t>8648297774</t>
   </si>
   <si>
     <t>CAMPO DESENHO FORNECIMENTO</t>
   </si>
   <si>
-    <t>30179</t>
+    <t>02/04/2025</t>
+  </si>
+  <si>
+    <t>8539909434</t>
   </si>
   <si>
     <t>Permissão Alteração Campo Modelo Cliente</t>
   </si>
   <si>
-    <t>30324</t>
+    <t>30/03/2025</t>
+  </si>
+  <si>
+    <t>8648185088</t>
   </si>
   <si>
     <t>Inclusão no Planilha do MPS</t>
   </si>
   <si>
-    <t>30081</t>
+    <t>8764226064</t>
   </si>
   <si>
     <t>INVENTÁRIO WMS</t>
   </si>
   <si>
-    <t>30572</t>
+    <t>26/03/2025</t>
+  </si>
+  <si>
+    <t>8753774663</t>
   </si>
   <si>
     <t>Alterações em gráficos de refugo - QlikSense</t>
   </si>
   <si>
-    <t>30587</t>
+    <t>8753685780</t>
   </si>
   <si>
     <t>Bloqueio de lançamento de frete sem conta contábil</t>
   </si>
   <si>
-    <t>30579</t>
+    <t>31/03/2025</t>
+  </si>
+  <si>
+    <t>8753730733</t>
   </si>
   <si>
     <t>APONTAMENTO JATO</t>
   </si>
   <si>
-    <t>30559</t>
+    <t>8753791402</t>
   </si>
   <si>
     <t>Projeto de tablet para empilhadeira de modelos - Reunião</t>
   </si>
   <si>
-    <t>30522</t>
+    <t>8753860845</t>
   </si>
   <si>
     <t>APONTAMENTO JATOS - SUGESTÕES DE MELHORIA</t>
   </si>
   <si>
-    <t>30679</t>
+    <t>8751772678</t>
   </si>
   <si>
     <t>CUSTOS LOGÍSTICOS - ALTERAÇÃO SERVIÇO NA ID</t>
   </si>
   <si>
-    <t>30521</t>
+    <t>8753910128</t>
   </si>
   <si>
     <t>Alterar o sistema de pré-lista EPI para considerar o saldo total - Validar</t>
   </si>
   <si>
-    <t>30659</t>
+    <t>8751790220</t>
   </si>
   <si>
     <t>Cópia do estoque almoxarifado para o WMS</t>
   </si>
   <si>
-    <t>30515</t>
+    <t>8753925361</t>
   </si>
   <si>
     <t>[MELHORIA] CRIAÇÃO CAMPO DE PIS e COFINS dentro do pedido de compra</t>
   </si>
   <si>
-    <t>30658</t>
+    <t>8751803202</t>
   </si>
   <si>
     <t>Saldo de estorno de requisição WMS</t>
   </si>
   <si>
-    <t>29788</t>
+    <t>8550212242</t>
   </si>
   <si>
     <t>CARACTERES CAMPO DE OBSERVAÇÃO - DESMOLDAGEM</t>
@@ -303,25 +327,25 @@
     <t>24/02/2025</t>
   </si>
   <si>
-    <t>30491</t>
+    <t>8754193713</t>
   </si>
   <si>
     <t>Solicitação de adição de campo para sequência digital no sistema WMS</t>
   </si>
   <si>
-    <t>30505</t>
+    <t>8754018042</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Cadastro de Materiais - Validação Família 90</t>
   </si>
   <si>
-    <t>30680</t>
+    <t>8751624984</t>
   </si>
   <si>
     <t>FORMULÁRIOS NÃO PREENCHIDOS E MOVIMENTADOS</t>
   </si>
   <si>
-    <t>30200</t>
+    <t>8539713193</t>
   </si>
   <si>
     <t>FTF x CPP</t>
@@ -330,6 +354,9 @@
     <t>30012</t>
   </si>
   <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
@@ -351,67 +378,67 @@
     <t>Incluir grupo de recurso no pré roteiro da AC</t>
   </si>
   <si>
-    <t>30434</t>
+    <t>8754393838</t>
   </si>
   <si>
     <t>Divergência sistema de corridas</t>
   </si>
   <si>
-    <t>30219</t>
+    <t>8540643947</t>
   </si>
   <si>
     <t>Registro na movimentação do setor 502</t>
   </si>
   <si>
-    <t>30483</t>
+    <t>8754277941</t>
   </si>
   <si>
     <t>AJUSTE DE ERROS E BUGS NO SISTEMA DE INVOICE - LANÇAMENTOS E RELATÓRIOS DE ID</t>
   </si>
   <si>
-    <t>30507</t>
+    <t>8753994276</t>
   </si>
   <si>
     <t>Grupo de maquina etiqueta azul</t>
   </si>
   <si>
-    <t>30611</t>
+    <t>8753618089</t>
   </si>
   <si>
     <t>Incluir filtro no IROG ACABAMENTO - "Estado da peça"</t>
   </si>
   <si>
-    <t>30641</t>
+    <t>8751847998</t>
   </si>
   <si>
     <t>BLOQUEIO USINAGEM TERCEIROS</t>
   </si>
   <si>
-    <t>30687</t>
+    <t>8751557035</t>
   </si>
   <si>
     <t>Relatório NFe Lançadas por Usuário</t>
   </si>
   <si>
-    <t>30062</t>
+    <t>8540434474</t>
   </si>
   <si>
     <t>Campo - Terceiros</t>
   </si>
   <si>
-    <t>30648</t>
+    <t>8751816418</t>
   </si>
   <si>
     <t>Ajustes IROG acabamento</t>
   </si>
   <si>
-    <t>30766</t>
+    <t>8774882654</t>
   </si>
   <si>
     <t>APONTAMENTO ELETRONICO MANIPULADOR</t>
   </si>
   <si>
-    <t>25/03/2025</t>
+    <t>8861288816</t>
   </si>
   <si>
     <t>Criação da tabela de imagens com a chave do modelo do depósito de modelos</t>
@@ -423,19 +450,22 @@
     <t>Abril</t>
   </si>
   <si>
+    <t>8861293478</t>
+  </si>
+  <si>
     <t>Criação do modelo do sistema em web</t>
   </si>
   <si>
-    <t>30907</t>
+    <t>8840300614</t>
   </si>
   <si>
     <t>P Number Solar - alteração</t>
   </si>
   <si>
-    <t>02/04/2025</t>
-  </si>
-  <si>
-    <t>26286</t>
+    <t>01/04/2025</t>
+  </si>
+  <si>
+    <t>6794417762</t>
   </si>
   <si>
     <t>Melhoria Sistema de Custeio - Cadastro Grupo de Clientes</t>
@@ -447,7 +477,7 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>24821</t>
+    <t>6348285779</t>
   </si>
   <si>
     <t>Segregar custeio do macroprocesso (área) Usinagem por Sub-área</t>
@@ -459,6 +489,9 @@
     <t>29853</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
   </si>
   <si>
@@ -471,7 +504,7 @@
     <t>ADH</t>
   </si>
   <si>
-    <t>26829</t>
+    <t>8754498311</t>
   </si>
   <si>
     <t>Segregar custeio do macroprocesso (área) Fundição por Sub-área</t>
@@ -486,13 +519,13 @@
     <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
   </si>
   <si>
-    <t>26830</t>
+    <t>8754797358</t>
   </si>
   <si>
     <t>Segregar custeio do macroprocesso (área) Acabamento por Sub-área</t>
   </si>
   <si>
-    <t>30581</t>
+    <t>8753701430</t>
   </si>
   <si>
     <t>INVENTÁRIO INTERMEDIARIO</t>
@@ -501,13 +534,13 @@
     <t>Fazendo</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>8764407220</t>
   </si>
   <si>
     <t>Ajustar o nome dos atributos nas tabelas YMS0 e YMS1</t>
   </si>
   <si>
-    <t>31015</t>
+    <t>8764738505</t>
   </si>
   <si>
     <t>Conversão KB18 - Importação de Objetos TRN, PRC e RPT</t>
@@ -519,7 +552,7 @@
     <t>Refinar o design do HUB</t>
   </si>
   <si>
-    <t>30154</t>
+    <t>8764407000</t>
   </si>
   <si>
     <t>Extração de Roteiros em massa</t>
@@ -528,7 +561,7 @@
     <t>Fila</t>
   </si>
   <si>
-    <t>25807</t>
+    <t>8754974818</t>
   </si>
   <si>
     <t>Visualização faseamento - Colunas com valores; apresentar no formato contábil.</t>
@@ -540,10 +573,13 @@
     <t>Implementar o carregamento de menus</t>
   </si>
   <si>
+    <t>8754972243</t>
+  </si>
+  <si>
     <t>Visualização faseamento - Incluir na tela todas as colunas existentes na planilha, exceto as colunas C [RAZÃO_SOCIAL] e G [PAÍS].</t>
   </si>
   <si>
-    <t>31011</t>
+    <t>8765570437</t>
   </si>
   <si>
     <t>Diário de bordo moldagem - Fast loop Carrosel e ULE</t>
@@ -555,13 +591,13 @@
     <t>Desenvolver o cadastro de categorias</t>
   </si>
   <si>
-    <t>28708</t>
+    <t>8765113039</t>
   </si>
   <si>
     <t>Bloco K Reroativo 2019/01 a 2023/09</t>
   </si>
   <si>
-    <t>25087</t>
+    <t>8754968903</t>
   </si>
   <si>
     <t>Verificar no cadastro do cliente a informação da moeda do cliente</t>
@@ -573,6 +609,9 @@
     <t>Implementar o carregamento de categorias</t>
   </si>
   <si>
+    <t>8754976142</t>
+  </si>
+  <si>
     <t>Visualização faseamento - A planilha para importação terá somente abas [Valor Original] e [Peso].</t>
   </si>
   <si>
@@ -582,9 +621,15 @@
     <t>Desenvolver o cadastro de menus</t>
   </si>
   <si>
+    <t>8754973832</t>
+  </si>
+  <si>
     <t>Visualização faseamento - Incluir filtro por [REGIÃO].</t>
   </si>
   <si>
+    <t>8754970806</t>
+  </si>
+  <si>
     <t>Visualização faseamento - Substituir o formato de paginação para scroll vertical.</t>
   </si>
   <si>
@@ -594,19 +639,19 @@
     <t>KB Modelo EV 18</t>
   </si>
   <si>
+    <t>8754965749</t>
+  </si>
+  <si>
     <t>Implementar o cadastro para novos registros</t>
   </si>
   <si>
-    <t>30158</t>
+    <t>8801339659</t>
   </si>
   <si>
     <t>CADASTRO DE DOCUMENTO NO SETOR 500</t>
   </si>
   <si>
-    <t>27/03/2025</t>
-  </si>
-  <si>
-    <t>30782</t>
+    <t>8804770745</t>
   </si>
   <si>
     <t>Diário de bordo - Correções visuais diário de bordo UPR</t>
@@ -615,12 +660,21 @@
     <t>28/03/2025</t>
   </si>
   <si>
+    <t>8804780297</t>
+  </si>
+  <si>
     <t>Diário de bordo - divisão de horários e metas por dia da semana</t>
   </si>
   <si>
+    <t>8804783735</t>
+  </si>
+  <si>
     <t>Diário de bordo - melhorias e correções no controle de paradas</t>
   </si>
   <si>
+    <t>8804786812</t>
+  </si>
+  <si>
     <t>Diário de bordo - rastreabilidade de usuários em paradas e apontamentos - UPR</t>
   </si>
   <si>
@@ -642,7 +696,7 @@
     <t>Conferência e levantamento de campos em branco na integração com APS no SQLServer</t>
   </si>
   <si>
-    <t>30975</t>
+    <t>8861233145</t>
   </si>
   <si>
     <t>Correção</t>
@@ -651,9 +705,15 @@
     <t>Relatório do PDI (PDI_ClientReportPDF_Seq)</t>
   </si>
   <si>
+    <t>8861240186</t>
+  </si>
+  <si>
     <t>PDI_InstrucaoAnalista</t>
   </si>
   <si>
+    <t>8861246323</t>
+  </si>
+  <si>
     <t>WWPDI_InspecaoReport</t>
   </si>
   <si>
@@ -669,7 +729,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-7</t>
+    <t>Mar/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -730,6 +790,9 @@
   </si>
   <si>
     <t>Baixa</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Não definida</t>
@@ -1305,13 +1368,13 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>34</v>
@@ -1352,13 +1415,13 @@
         <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>39</v>
@@ -1399,13 +1462,13 @@
         <v>44</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>39</v>
@@ -1416,7 +1479,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1428,10 +1491,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1446,13 +1509,13 @@
         <v>31</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>34</v>
@@ -1463,7 +1526,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1475,10 +1538,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1493,7 +1556,7 @@
         <v>44</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1510,7 +1573,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1522,10 +1585,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1540,13 +1603,13 @@
         <v>31</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>34</v>
@@ -1557,22 +1620,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>43</v>
@@ -1587,10 +1650,10 @@
         <v>44</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>26</v>
@@ -1604,7 +1667,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1616,10 +1679,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1634,10 +1697,10 @@
         <v>31</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>26</v>
@@ -1651,7 +1714,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1663,10 +1726,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1678,13 +1741,13 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>26</v>
@@ -1698,7 +1761,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1710,10 +1773,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1728,7 +1791,7 @@
         <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1745,7 +1808,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1757,10 +1820,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1775,7 +1838,7 @@
         <v>31</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1792,7 +1855,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1804,10 +1867,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1822,7 +1885,7 @@
         <v>23</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1839,7 +1902,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1851,10 +1914,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1866,13 +1929,13 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>26</v>
@@ -1886,7 +1949,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1898,10 +1961,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1919,7 +1982,7 @@
         <v>24</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>26</v>
@@ -1933,7 +1996,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1945,10 +2008,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1963,10 +2026,10 @@
         <v>44</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>26</v>
@@ -1980,7 +2043,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1992,10 +2055,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -2010,10 +2073,10 @@
         <v>31</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>26</v>
@@ -2027,7 +2090,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -2039,10 +2102,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -2057,10 +2120,10 @@
         <v>31</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>26</v>
@@ -2074,7 +2137,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2086,10 +2149,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2104,10 +2167,10 @@
         <v>31</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>26</v>
@@ -2121,22 +2184,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2151,10 +2214,10 @@
         <v>31</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>26</v>
@@ -2168,7 +2231,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2180,10 +2243,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2198,10 +2261,10 @@
         <v>31</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>26</v>
@@ -2215,7 +2278,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2227,10 +2290,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2245,10 +2308,10 @@
         <v>31</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>26</v>
@@ -2262,7 +2325,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2274,10 +2337,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2292,10 +2355,10 @@
         <v>31</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>26</v>
@@ -2309,7 +2372,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2321,10 +2384,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2339,10 +2402,10 @@
         <v>31</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>26</v>
@@ -2356,7 +2419,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2368,10 +2431,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2386,10 +2449,10 @@
         <v>31</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>26</v>
@@ -2403,7 +2466,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2415,10 +2478,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2433,10 +2496,10 @@
         <v>31</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>26</v>
@@ -2450,7 +2513,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2462,10 +2525,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>43</v>
@@ -2477,13 +2540,13 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>26</v>
@@ -2497,7 +2560,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2509,10 +2572,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2527,10 +2590,10 @@
         <v>31</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>26</v>
@@ -2544,7 +2607,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2556,10 +2619,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2574,10 +2637,10 @@
         <v>31</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>26</v>
@@ -2591,7 +2654,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2603,10 +2666,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2621,7 +2684,7 @@
         <v>31</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2638,7 +2701,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2650,10 +2713,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2665,10 +2728,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2685,37 +2748,37 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2732,37 +2795,37 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2779,7 +2842,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2791,10 +2854,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2809,10 +2872,10 @@
         <v>31</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>26</v>
@@ -2826,7 +2889,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2838,10 +2901,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2853,10 +2916,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2873,7 +2936,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2885,10 +2948,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2903,10 +2966,10 @@
         <v>31</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>26</v>
@@ -2920,7 +2983,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2932,10 +2995,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2950,7 +3013,7 @@
         <v>31</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2967,7 +3030,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2979,10 +3042,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>43</v>
@@ -2997,10 +3060,10 @@
         <v>31</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>26</v>
@@ -3014,7 +3077,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -3026,10 +3089,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -3044,10 +3107,10 @@
         <v>31</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>26</v>
@@ -3061,7 +3124,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -3073,10 +3136,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3091,10 +3154,10 @@
         <v>31</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>26</v>
@@ -3108,7 +3171,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3120,10 +3183,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3135,13 +3198,13 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>26</v>
@@ -3155,7 +3218,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3167,10 +3230,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3185,10 +3248,10 @@
         <v>31</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>26</v>
@@ -3202,7 +3265,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3214,10 +3277,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3229,13 +3292,13 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>26</v>
@@ -3249,22 +3312,22 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3276,13 +3339,13 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>26</v>
@@ -3291,27 +3354,27 @@
         <v>27</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3323,13 +3386,13 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>26</v>
@@ -3338,12 +3401,12 @@
         <v>27</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3355,10 +3418,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3370,13 +3433,13 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>26</v>
@@ -3385,12 +3448,12 @@
         <v>27</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3402,10 +3465,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3417,27 +3480,27 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3449,10 +3512,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3464,16 +3527,16 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>39</v>
@@ -3484,40 +3547,40 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>44</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>26</v>
@@ -3531,7 +3594,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3543,10 +3606,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3561,13 +3624,13 @@
         <v>31</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>34</v>
@@ -3578,40 +3641,40 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>44</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>26</v>
@@ -3625,7 +3688,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3637,10 +3700,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3655,13 +3718,13 @@
         <v>31</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>34</v>
@@ -3672,7 +3735,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3684,10 +3747,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3702,13 +3765,13 @@
         <v>31</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>34</v>
@@ -3719,7 +3782,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3731,10 +3794,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3749,10 +3812,10 @@
         <v>44</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>26</v>
@@ -3766,22 +3829,22 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3796,10 +3859,10 @@
         <v>44</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M56" s="2" t="s">
         <v>26</v>
@@ -3813,7 +3876,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3825,10 +3888,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3843,10 +3906,10 @@
         <v>38</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M57" s="2" t="s">
         <v>26</v>
@@ -3860,7 +3923,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3872,10 +3935,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -3890,13 +3953,13 @@
         <v>44</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>39</v>
@@ -3907,22 +3970,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>43</v>
@@ -3937,10 +4000,10 @@
         <v>31</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>26</v>
@@ -3954,7 +4017,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -3966,10 +4029,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -3984,10 +4047,10 @@
         <v>38</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>26</v>
@@ -4001,22 +4064,22 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>43</v>
@@ -4031,10 +4094,10 @@
         <v>31</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M61" s="2" t="s">
         <v>26</v>
@@ -4048,22 +4111,22 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>43</v>
@@ -4078,10 +4141,10 @@
         <v>44</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>26</v>
@@ -4095,7 +4158,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4107,10 +4170,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4125,10 +4188,10 @@
         <v>38</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>26</v>
@@ -4142,7 +4205,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4154,10 +4217,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4172,10 +4235,10 @@
         <v>44</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>26</v>
@@ -4189,22 +4252,22 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>43</v>
@@ -4219,13 +4282,13 @@
         <v>31</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>34</v>
@@ -4236,7 +4299,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4248,10 +4311,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4266,10 +4329,10 @@
         <v>38</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>26</v>
@@ -4283,22 +4346,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>43</v>
@@ -4313,13 +4376,13 @@
         <v>31</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>34</v>
@@ -4330,7 +4393,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4342,10 +4405,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4360,10 +4423,10 @@
         <v>38</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>26</v>
@@ -4377,22 +4440,22 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>43</v>
@@ -4407,10 +4470,10 @@
         <v>31</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>26</v>
@@ -4424,22 +4487,22 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>43</v>
@@ -4454,10 +4517,10 @@
         <v>31</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>26</v>
@@ -4471,7 +4534,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
@@ -4483,10 +4546,10 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>43</v>
@@ -4501,10 +4564,10 @@
         <v>44</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>26</v>
@@ -4518,22 +4581,22 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>43</v>
@@ -4548,13 +4611,13 @@
         <v>31</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>34</v>
@@ -4565,7 +4628,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
@@ -4577,10 +4640,10 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4592,16 +4655,16 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>196</v>
+        <v>64</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>39</v>
@@ -4612,7 +4675,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
@@ -4624,10 +4687,10 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
@@ -4639,13 +4702,13 @@
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M74" s="2" t="s">
         <v>26</v>
@@ -4659,7 +4722,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
@@ -4671,10 +4734,10 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>43</v>
@@ -4686,13 +4749,13 @@
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M75" s="2" t="s">
         <v>26</v>
@@ -4706,7 +4769,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
@@ -4718,10 +4781,10 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>43</v>
@@ -4733,13 +4796,13 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>26</v>
@@ -4753,7 +4816,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
@@ -4765,10 +4828,10 @@
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>43</v>
@@ -4780,13 +4843,13 @@
         <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>26</v>
@@ -4800,40 +4863,40 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>26</v>
@@ -4842,45 +4905,45 @@
         <v>27</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>26</v>
@@ -4889,45 +4952,45 @@
         <v>27</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>26</v>
@@ -4936,45 +4999,45 @@
         <v>27</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M81" s="2" t="s">
         <v>26</v>
@@ -4983,45 +5046,45 @@
         <v>27</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M82" s="2" t="s">
         <v>26</v>
@@ -5030,45 +5093,45 @@
         <v>27</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M83" s="2" t="s">
         <v>26</v>
@@ -5077,27 +5140,27 @@
         <v>27</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
@@ -5109,13 +5172,13 @@
         <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>26</v>
@@ -5124,27 +5187,27 @@
         <v>27</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
@@ -5156,42 +5219,42 @@
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
@@ -5203,13 +5266,13 @@
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M86" s="2" t="s">
         <v>26</v>
@@ -5218,12 +5281,12 @@
         <v>27</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>16</v>
@@ -5235,10 +5298,10 @@
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>43</v>
@@ -5253,10 +5316,10 @@
         <v>44</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M87" s="2" t="s">
         <v>26</v>
@@ -5281,23 +5344,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="D2" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="E2" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5305,16 +5368,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5325,20 +5388,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>416.44</v>
+        <v>64.94</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K22">
         <v>59</v>
@@ -5354,7 +5417,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5385,12 +5448,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="B2">
         <v>86</v>
@@ -5404,35 +5467,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>416.44</v>
+        <v>64.94</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5440,7 +5503,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -5449,19 +5512,19 @@
         <v>62</v>
       </c>
       <c r="G10" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N10">
         <v>59</v>
@@ -5470,12 +5533,18 @@
         <v>27</v>
       </c>
       <c r="Q10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E11">
         <v>14</v>
@@ -5490,10 +5559,10 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N11">
         <v>10</v>
@@ -5502,10 +5571,16 @@
         <v>34</v>
       </c>
       <c r="Q11">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
       <c r="D12" t="s">
         <v>36</v>
       </c>
@@ -5519,13 +5594,13 @@
         <v>69</v>
       </c>
       <c r="J12" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="K12">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -5534,32 +5609,38 @@
         <v>39</v>
       </c>
       <c r="Q12">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="N13">
         <v>4</v>
       </c>
+      <c r="P13" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q13">
+        <v>9</v>
+      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5573,7 +5654,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -5581,7 +5662,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -5589,7 +5670,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5597,10 +5678,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -5608,7 +5689,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5616,142 +5697,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>409</v>
+        <v>797</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>409</v>
+        <v>797</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>407</v>
+        <v>797</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>148</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>398</v>
+        <v>797</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>398</v>
+        <v>797</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>204</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>398</v>
+        <v>797</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>398</v>
+        <v>797</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>206</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>398</v>
+        <v>797</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>398</v>
+        <v>797</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
